--- a/amd/dist/20261025_AMD模型_v0.1.xlsx
+++ b/amd/dist/20261025_AMD模型_v0.1.xlsx
@@ -3625,7 +3625,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -3644,7 +3644,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3918,7 +3918,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -3937,7 +3937,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4215,7 +4215,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4234,7 +4234,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4366,7 +4366,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4385,7 +4385,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4537,7 +4537,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4556,7 +4556,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4688,7 +4688,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4707,7 +4707,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4850,7 +4850,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4869,7 +4869,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5077,7 +5077,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -5096,7 +5096,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5289,7 +5289,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -5308,7 +5308,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5440,7 +5440,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -5459,7 +5459,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5697,7 +5697,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -5716,7 +5716,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5848,7 +5848,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -5867,7 +5867,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6010,7 +6010,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -6029,7 +6029,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6161,7 +6161,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -6180,7 +6180,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6401,7 +6401,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -6420,7 +6420,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6769,7 +6769,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -6788,7 +6788,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6893,7 +6893,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -6912,7 +6912,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7111,7 +7111,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7130,7 +7130,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7232,7 +7232,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7251,7 +7251,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7353,7 +7353,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7372,7 +7372,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7474,7 +7474,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7493,7 +7493,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7595,7 +7595,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7614,7 +7614,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8013,7 +8013,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -8032,7 +8032,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8137,7 +8137,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -8156,7 +8156,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8261,7 +8261,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -8280,7 +8280,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8460,7 +8460,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -8479,7 +8479,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8583,7 +8583,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -8602,7 +8602,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8849,7 +8849,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -8868,7 +8868,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8991,7 +8991,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9010,7 +9010,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9161,7 +9161,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9180,7 +9180,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9441,7 +9441,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9460,7 +9460,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9631,7 +9631,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9650,7 +9650,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9743,7 +9743,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9762,7 +9762,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9855,7 +9855,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9874,7 +9874,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9967,7 +9967,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -9986,7 +9986,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10079,7 +10079,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10098,7 +10098,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10191,7 +10191,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10210,7 +10210,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10303,7 +10303,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10322,7 +10322,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10415,7 +10415,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10434,7 +10434,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10527,7 +10527,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10546,7 +10546,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10639,7 +10639,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10658,7 +10658,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10751,7 +10751,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">nvidia/dist/20261023_NVIDIA</t>
+      <t xml:space="preserve">nvidia/dist/20261025_NVIDIA</t>
     </r>
     <r>
       <rPr>
@@ -10770,7 +10770,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/amd/dist/20261025_AMD模型_v0.1.xlsx
+++ b/amd/dist/20261025_AMD模型_v0.1.xlsx
@@ -3644,7 +3644,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3937,7 +3937,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4234,7 +4234,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4385,7 +4385,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4556,7 +4556,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4707,7 +4707,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4869,7 +4869,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5096,7 +5096,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5308,7 +5308,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5459,7 +5459,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5716,7 +5716,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5867,7 +5867,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6029,7 +6029,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6180,7 +6180,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6420,7 +6420,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6788,7 +6788,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6912,7 +6912,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7130,7 +7130,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7251,7 +7251,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7372,7 +7372,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7493,7 +7493,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7614,7 +7614,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
